--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2020/NEW_JERSEY_2020.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2020/NEW_JERSEY_2020.xlsx
@@ -1572,7 +1572,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C68">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C172">
@@ -3588,7 +3588,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C180">
@@ -8520,7 +8520,7 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Putla Villa De Guerero</t>
+          <t>Putla Villa De Guerrero</t>
         </is>
       </c>
       <c r="C454">
@@ -10068,7 +10068,7 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C540">
@@ -10086,7 +10086,7 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 26 -</t>
+          <t>San Pedro Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C541">
@@ -12354,7 +12354,7 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>Ayotoxco De Guerero</t>
+          <t>Ayotoxco De Guerrero</t>
         </is>
       </c>
       <c r="C667">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>Ixcamilpa De Guerero</t>
+          <t>Ixcamilpa De Guerrero</t>
         </is>
       </c>
       <c r="C712">
@@ -14766,7 +14766,7 @@
       </c>
       <c r="B801" t="inlineStr">
         <is>
-          <t>Totoltepec De Guerero</t>
+          <t>Totoltepec De Guerrero</t>
         </is>
       </c>
       <c r="C801">
@@ -14838,7 +14838,7 @@
       </c>
       <c r="B805" t="inlineStr">
         <is>
-          <t>Vicente Guerero</t>
+          <t>Vicente Guerrero</t>
         </is>
       </c>
       <c r="C805">
